--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,24 @@
   </si>
   <si>
     <t>实体.xlsx</t>
+  </si>
+  <si>
+    <t>Scene.TbSceneConfig</t>
+  </si>
+  <si>
+    <t>SceneConfig</t>
+  </si>
+  <si>
+    <t>场景.xlsx</t>
+  </si>
+  <si>
+    <t>Actor.TbActorConfig</t>
+  </si>
+  <si>
+    <t>ActorConfig</t>
+  </si>
+  <si>
+    <t>角色.xlsx</t>
   </si>
 </sst>
 </file>
@@ -747,7 +765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -758,9 +776,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,8 +1097,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1183,16 +1198,16 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:11">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1208,6 +1223,34 @@
       </c>
       <c r="E5" s="3" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
